--- a/data/export/2026-10-03-浦东35路.xlsx
+++ b/data/export/2026-10-03-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/21</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/21</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/21</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/21</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/21</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/21</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/21</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/21</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1603,1339 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东35路.xlsx
+++ b/data/export/2026-10-03-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1100,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1109,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,33 +1161,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1635,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1746,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1857,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1968,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2029,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2079,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2140,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2190,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2251,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2301,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2362,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2412,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2473,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2523,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2584,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2634,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2695,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2745,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2806,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2824,7 +2856,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2917,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2935,7 +2967,1129 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东35路.xlsx
+++ b/data/export/2026-10-03-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,10 +446,10 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>125.0</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -989,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1110,24 +1118,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1137,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1186,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1252,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1402,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1413,7 +1429,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1513,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1524,7 +1540,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1552,32 +1568,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1585,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1609,17 +1629,17 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1629,13 +1649,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1687,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>119分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1696,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,33 +1748,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -1774,32 +1806,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1807,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1831,17 +1867,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1851,13 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1925,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq51，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1918,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1926,10 +1966,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±3分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -1968,7 +2024,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2079,7 +2135,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2190,7 +2246,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2274,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq39推进至seq47，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2251,18 +2307,30 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>沪南路华夏西路</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>08:03</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
       <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq21映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2301,7 +2369,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2412,7 +2480,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2591,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2652,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2634,7 +2702,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2763,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2745,7 +2813,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2874,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2856,7 +2924,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2985,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2967,7 +3035,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3096,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3078,7 +3146,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3207,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3189,7 +3257,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3318,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3300,7 +3368,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3429,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3411,7 +3479,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3540,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3522,7 +3590,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3651,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3633,7 +3701,7 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3762,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3748,7 +3816,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3877,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3863,7 +3931,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3992,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3974,7 +4042,7 @@
       <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3982,22 +4050,22 @@
       <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4035,7 +4103,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4084,12 +4152,805 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东35路.xlsx
+++ b/data/export/2026-10-03-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,14 +1644,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1816,24 +1816,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq51，推进13站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq55，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2163,32 +2163,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2196,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2220,33 +2224,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2287,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq39推进至seq47，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq39推进至seq55，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2307,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2430,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2652,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2763,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2874,7 +2882,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2985,7 +2993,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3096,7 +3104,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,7 +3215,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,7 +3326,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,7 +3437,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3540,7 +3548,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3651,7 +3659,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3762,7 +3770,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3877,7 +3885,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3992,7 +4000,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4103,7 +4111,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4218,7 +4226,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4272,7 +4280,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4333,7 +4341,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4387,7 +4395,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4456,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4563,7 +4571,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4674,7 +4682,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4785,7 +4793,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4843,22 +4851,22 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4891,12 +4899,12 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4945,12 +4953,242 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>119.0</t>
         </is>
       </c>
-      <c r="AC39" s="2" t="inlineStr">
+      <c r="AC40" s="2" t="inlineStr">
         <is>
           <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东35路.xlsx
+++ b/data/export/2026-10-03-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC41"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,14 +1882,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq39推进至seq55，推进16站，达到≥2站确认条件</t>
+          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq39推进至seq62，推进23站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2405,32 +2405,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2438,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2462,33 +2466,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2699,7 +2707,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2738,32 +2746,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2771,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2795,33 +2807,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2898,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2921,7 +2937,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2960,32 +2976,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2993,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3017,33 +3037,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3071,32 +3095,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3104,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3128,17 +3156,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3148,13 +3176,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3182,32 +3214,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3215,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3239,33 +3275,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3293,32 +3333,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3326,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3350,17 +3394,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3370,13 +3414,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3404,32 +3452,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3437,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3461,17 +3513,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3481,13 +3533,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3659,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3770,7 +3826,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,7 +3941,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4000,7 +4056,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4111,7 +4167,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4226,7 +4282,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4280,7 +4336,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4397,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4395,7 +4451,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4512,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4571,7 +4627,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4682,7 +4738,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4793,7 +4849,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4904,7 +4960,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4958,7 +5014,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5075,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5081,22 +5137,22 @@
       <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5129,12 +5185,12 @@
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5188,6 +5244,914 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
           <t>6/29</t>
         </is>
       </c>

--- a/data/export/2026-10-03-浦东35路.xlsx
+++ b/data/export/2026-10-03-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,13 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,18 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1659,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1843,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2496,7 +2504,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2783,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2837,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3013,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3067,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3305,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3409,14 +3417,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -3424,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3462,24 +3470,24 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3489,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3538,12 +3546,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3571,32 +3579,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3604,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3628,17 +3640,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3648,13 +3660,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3682,32 +3698,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3715,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3739,33 +3759,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3793,32 +3817,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3826,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3850,37 +3878,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3908,32 +3936,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3941,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3965,17 +3997,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3985,17 +4017,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4023,32 +4055,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -4056,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4080,33 +4116,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4134,32 +4174,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4167,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4191,17 +4235,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4211,17 +4255,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4249,32 +4293,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4282,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4306,37 +4354,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4364,32 +4412,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4397,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4421,17 +4473,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4441,17 +4493,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4479,32 +4531,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4512,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4536,37 +4592,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4594,32 +4650,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4627,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4651,33 +4711,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB36" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4705,32 +4769,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4738,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4762,17 +4830,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4782,13 +4850,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB37" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4960,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5014,7 +5086,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5147,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5190,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5244,7 +5316,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5377,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5359,7 +5431,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5492,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5531,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5585,7 +5657,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5718,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5757,7 +5829,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5811,7 +5883,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5944,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5983,7 +6055,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6037,7 +6109,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6170,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6152,7 +6224,812 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东35路.xlsx
+++ b/data/export/2026-10-03-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,22 +1652,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,18 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2262,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2378,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2450,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2494,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2719,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2791,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,17 +2839,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3021,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3075,7 +3079,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3378,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3432,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3555,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3789,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4027,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4330,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4384,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4687,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4741,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4888,12 +4892,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq56推进至seq62，推进6站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4921,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4929,10 +4933,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="inlineStr"/>
-      <c r="T38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq22映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
           <t>09:38</t>
@@ -4960,7 +4976,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4999,32 +5015,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -5032,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5056,37 +5076,37 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5114,32 +5134,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>118分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5147,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5171,17 +5195,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5191,12 +5215,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5229,32 +5253,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5262,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5286,17 +5314,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5306,17 +5334,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5431,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5459,32 +5487,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5492,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5516,33 +5548,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5570,32 +5606,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5603,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5627,17 +5667,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5647,17 +5687,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5757,7 +5797,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5796,32 +5836,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5829,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5853,17 +5897,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5873,17 +5917,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6055,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6109,7 +6153,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6285,7 +6329,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6339,7 +6383,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6454,7 +6498,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6515,7 +6559,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6630,7 +6674,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6745,7 +6789,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6799,7 +6843,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6904,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6975,7 +7019,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7029,7 +7073,681 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东35路.xlsx
+++ b/data/export/2026-10-03-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,14 +2493,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>129.5</t>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2724,13 +2724,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,12 +2848,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,13 +2958,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3064,22 +3072,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3302,22 +3310,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3426,17 +3434,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3682,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,22 +3786,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3897,7 +3905,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3912,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4150,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4378,17 +4386,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4626,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4745,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5052,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5106,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5578,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5682,14 +5690,14 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
           <t>129.5</t>
@@ -5697,7 +5705,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5733,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5758,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5782,17 +5794,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5802,13 +5814,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5862,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -5873,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5922,12 +5938,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5955,32 +5971,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5988,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6012,17 +6032,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6032,13 +6052,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6066,32 +6090,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -6099,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6123,37 +6151,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6181,32 +6209,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6214,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6238,37 +6270,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6296,32 +6328,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6329,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6353,17 +6389,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6373,17 +6409,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6411,32 +6447,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6444,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6468,37 +6508,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6598,7 +6638,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6613,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6728,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6756,32 +6796,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6789,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6813,17 +6857,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6833,17 +6877,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6958,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7073,7 +7117,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7245,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7299,7 +7343,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7404,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7471,7 +7515,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7525,7 +7569,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7630,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7697,7 +7741,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7741,13 +7785,592 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB62" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东35路.xlsx
+++ b/data/export/2026-10-03-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>128.5</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,14 +1303,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>134.5</t>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,18 +2021,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2266,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2454,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2853,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3087,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3444,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3548,14 +3552,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -3563,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3801,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3985,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,14 +4028,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>128.5</t>
@@ -4039,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4148,17 +4152,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,17 +4385,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4461,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,14 +4504,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>134.5</t>
@@ -4515,7 +4519,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4624,17 +4628,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,22 +4742,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5060,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5114,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5651,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5705,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5943,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6181,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6419,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6538,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6681,32 +6685,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6714,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6738,17 +6746,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6758,17 +6766,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6806,12 +6814,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -6833,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6872,17 +6880,17 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6915,32 +6923,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6948,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6972,17 +6984,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6992,17 +7004,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7030,32 +7042,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7063,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7087,37 +7103,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7161,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq37推进至seq51，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7178,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7186,10 +7202,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q57" s="2" t="inlineStr"/>
-      <c r="R57" s="2" t="inlineStr"/>
-      <c r="S57" s="2" t="inlineStr"/>
-      <c r="T57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq22映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±6分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
           <t>12:28</t>
@@ -7289,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7343,7 +7375,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7371,32 +7403,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7404,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7428,33 +7464,37 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7630,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7741,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7856,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7910,7 +7950,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7971,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8086,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8140,7 +8180,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8316,7 +8356,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8370,7 +8410,697 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
+          <t>25/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
           <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东35路.xlsx
+++ b/data/export/2026-10-03-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC73"/>
+  <dimension ref="A1:AC78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2387,13 +2387,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2502,17 +2506,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,17 +2732,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3091,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,14 +3199,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>126.0</t>
@@ -3210,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3448,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3567,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,14 +3675,14 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
@@ -3686,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3805,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3924,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4043,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4400,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4519,7 +4523,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4757,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,7 +4992,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5064,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5108,17 +5112,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5222,7 +5226,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5356,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5456,7 +5460,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5471,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5580,7 +5584,7 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
@@ -5590,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5699,17 +5703,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5818,17 +5822,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6185,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6423,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6542,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6657,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6895,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7133,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7170,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq37推进至seq51，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq37推进至seq57，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7194,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7249,7 +7253,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7288,32 +7292,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7321,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7345,17 +7353,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7365,17 +7373,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -7413,24 +7421,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7440,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7489,12 +7497,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -7522,32 +7530,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7555,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7579,17 +7591,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7599,7 +7611,7 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
@@ -7609,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7637,32 +7649,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7670,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7694,17 +7710,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7714,13 +7730,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB61" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7748,32 +7768,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7781,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7805,17 +7829,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7825,17 +7849,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7863,32 +7887,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7896,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7920,17 +7948,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7940,17 +7968,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8126,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8180,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8295,7 +8323,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8410,7 +8438,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8525,7 +8553,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8640,7 +8668,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8755,7 +8783,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8816,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8870,7 +8898,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8985,7 +9013,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -8993,22 +9021,22 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9041,12 +9069,12 @@
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9060,47 +9088,618 @@
       <c r="T73" s="2" t="inlineStr"/>
       <c r="U73" s="2" t="inlineStr">
         <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
           <t>15:25</t>
         </is>
       </c>
-      <c r="V73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W73" s="2" t="inlineStr">
+      <c r="W74" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X73" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y73" s="2" t="inlineStr">
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z73" s="2" t="inlineStr">
+      <c r="Z74" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
+      <c r="AA74" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>118.5</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
         </is>
       </c>
-      <c r="AC73" s="2" t="inlineStr">
-        <is>
-          <t>10/29</t>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东35路.xlsx
+++ b/data/export/2026-10-03-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC78"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>124.5</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,14 +1065,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>126.3</t>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,14 +1890,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2511,12 +2511,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3085,17 +3085,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3323,17 +3323,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3561,17 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3799,17 +3799,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>125.5</t>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,14 +4270,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>124.5</t>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4394,17 +4394,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4627,14 +4627,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>126.3</t>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,14 +5345,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6179,17 +6179,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6298,17 +6298,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6536,17 +6536,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6651,17 +6651,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6765,14 +6765,14 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
           <t>125.5</t>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6889,17 +6889,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7003,14 +7003,14 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
           <t>126.3</t>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7897,24 +7897,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8006,32 +8006,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8039,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8063,17 +8067,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8083,17 +8087,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -8121,32 +8125,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -8154,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8178,17 +8186,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8198,17 +8206,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8236,32 +8244,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8269,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8293,17 +8305,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8313,17 +8325,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8351,32 +8363,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8384,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8408,17 +8424,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8428,17 +8444,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -8466,32 +8482,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8499,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8523,17 +8543,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8543,17 +8563,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -8581,32 +8601,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8614,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8638,17 +8662,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8658,17 +8682,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8783,7 +8807,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8898,7 +8922,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9074,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9185,7 +9209,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9239,7 +9263,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9324,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9415,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9469,7 +9493,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9645,7 +9669,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9699,7 +9723,927 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>126.3</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东35路.xlsx
+++ b/data/export/2026-10-03-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:AC93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>129.2</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>119.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,22 +2021,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,14 +3556,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>134.5</t>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,22 +4032,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>129.2</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4508,17 +4508,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4751,17 +4751,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>119.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>129.2</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7127,17 +7127,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7487,22 +7487,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8558,14 +8558,14 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
           <t>134.5</t>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -8611,24 +8611,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8687,12 +8687,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>129.2</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8720,32 +8720,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8753,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8777,37 +8781,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8835,32 +8839,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8868,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8892,17 +8900,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8912,17 +8920,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8950,32 +8958,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8983,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9007,32 +9019,32 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9065,12 +9077,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq59，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -9098,7 +9110,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9106,10 +9118,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q73" s="2" t="inlineStr"/>
-      <c r="R73" s="2" t="inlineStr"/>
-      <c r="S73" s="2" t="inlineStr"/>
-      <c r="T73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
           <t>15:22</t>
@@ -9176,32 +9204,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9209,7 +9241,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9233,37 +9265,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -9291,32 +9323,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -9324,7 +9360,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9348,17 +9384,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9368,12 +9404,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>119.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9439,7 +9475,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9554,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9669,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9784,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9899,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10014,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10068,7 +10104,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10165,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10244,7 +10280,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10359,7 +10395,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10474,7 +10510,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10589,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10643,7 +10679,812 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>133.7</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东35路.xlsx
+++ b/data/export/2026-10-03-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC93"/>
+  <dimension ref="A1:AC100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>119.3</t>
+          <t>118.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2387,17 +2387,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2501,14 +2501,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>129.7</t>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,22 +3199,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,14 +3318,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>125.0</t>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,22 +3675,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,17 +5226,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>119.3</t>
+          <t>118.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5465,17 +5465,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,14 +5698,14 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
           <t>129.7</t>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6293,14 +6293,14 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>125.0</t>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7497,12 +7497,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7730,17 +7730,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7963,14 +7963,14 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
           <t>129.7</t>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8082,14 +8082,14 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
           <t>125.0</t>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8692,7 +8692,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9214,24 +9214,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -9333,24 +9333,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>118分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9399,17 +9399,17 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>119.3</t>
+          <t>118.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9442,32 +9442,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9475,7 +9479,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9499,37 +9503,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9557,32 +9561,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9590,7 +9598,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9614,37 +9622,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -9672,32 +9680,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9705,7 +9717,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9729,17 +9741,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9749,17 +9761,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9787,32 +9799,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9820,7 +9836,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9844,17 +9860,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9864,17 +9880,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9989,7 +10005,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10066,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10104,7 +10120,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -10132,32 +10148,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10165,7 +10185,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10189,17 +10209,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10209,12 +10229,12 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10280,7 +10300,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10334,7 +10354,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -10395,7 +10415,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10449,7 +10469,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10564,7 +10584,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10645,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10679,7 +10699,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10855,7 +10875,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10970,7 +10990,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11085,7 +11105,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11139,7 +11159,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11220,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11254,7 +11274,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -11315,7 +11335,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11430,7 +11450,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11479,12 +11499,813 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr"/>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>129.7</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>118.3</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东35路.xlsx
+++ b/data/export/2026-10-03-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC100"/>
+  <dimension ref="A1:AC108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,14 +3080,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>128.7</t>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,17 +3437,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3561,17 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,22 +4151,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,17 +4270,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,22 +4865,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5112,17 +5112,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5350,17 +5350,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6174,14 +6174,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>128.7</t>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6412,17 +6412,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6765,22 +6765,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7373,17 +7373,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8201,14 +8201,14 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
           <t>128.7</t>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8563,17 +8563,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -10033,32 +10033,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10066,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10090,32 +10094,32 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10158,12 +10162,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
@@ -10185,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10224,17 +10228,17 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10267,32 +10271,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10300,7 +10308,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10324,37 +10332,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -10382,32 +10390,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -10415,7 +10427,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10439,37 +10451,37 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -10497,32 +10509,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10530,7 +10546,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10554,17 +10570,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10574,12 +10590,12 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10612,32 +10628,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10645,7 +10665,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10669,17 +10689,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10689,17 +10709,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -10727,32 +10747,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10760,7 +10784,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10784,17 +10808,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10804,17 +10828,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -10842,32 +10866,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10875,7 +10903,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10899,17 +10927,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10919,17 +10947,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -10990,7 +11018,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11044,7 +11072,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11133,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11220,7 +11248,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11335,7 +11363,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11389,7 +11417,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -11450,7 +11478,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11504,7 +11532,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11676,7 +11704,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11730,7 +11758,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11819,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11845,7 +11873,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -11906,7 +11934,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12021,7 +12049,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12136,7 +12164,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12198,22 +12226,22 @@
       <c r="A100" s="2" t="inlineStr"/>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -12246,12 +12274,12 @@
       <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12265,47 +12293,967 @@
       <c r="T100" s="2" t="inlineStr"/>
       <c r="U100" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="V100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W100" s="2" t="inlineStr">
+      <c r="W101" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X100" s="2" t="inlineStr">
+      <c r="X101" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y100" s="2" t="inlineStr">
+      <c r="Y101" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z100" s="2" t="inlineStr">
+      <c r="Z101" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA100" s="2" t="inlineStr">
+      <c r="AA101" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB100" s="2" t="inlineStr">
+      <c r="AB101" s="2" t="inlineStr">
         <is>
           <t>127.5</t>
         </is>
       </c>
-      <c r="AC100" s="2" t="inlineStr">
+      <c r="AC101" s="2" t="inlineStr">
         <is>
           <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>128.7</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东35路.xlsx
+++ b/data/export/2026-10-03-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC108"/>
+  <dimension ref="A1:AC110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2732,17 +2732,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,22 +2961,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3204,17 +3204,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4513,17 +4513,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5584,17 +5584,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5822,17 +5822,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6055,22 +6055,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7611,17 +7611,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7849,17 +7849,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8801,17 +8801,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9039,17 +9039,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -10189,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10427,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10757,12 +10757,12 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10876,24 +10876,24 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10952,12 +10952,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -10985,32 +10985,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11018,7 +11022,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11042,17 +11046,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11062,17 +11066,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -11100,32 +11104,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11133,7 +11141,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11157,17 +11165,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11177,17 +11185,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -11215,32 +11223,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11248,7 +11260,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11272,17 +11284,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11292,17 +11304,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -11330,32 +11342,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11363,7 +11379,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11387,17 +11403,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11407,17 +11423,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -11532,7 +11548,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -11560,12 +11576,12 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq37推进至seq58，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -11593,7 +11609,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11601,10 +11617,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q94" s="2" t="inlineStr"/>
-      <c r="R94" s="2" t="inlineStr"/>
-      <c r="S94" s="2" t="inlineStr"/>
-      <c r="T94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>沪南路高科西路</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq25映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置浦建路锦绣路 ETA 17分钟参与校验</t>
+        </is>
+      </c>
       <c r="U94" s="2" t="inlineStr">
         <is>
           <t>18:12</t>
@@ -11671,32 +11703,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11704,7 +11740,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11728,37 +11764,37 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -11786,32 +11822,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11819,7 +11859,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11843,17 +11883,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11863,12 +11903,12 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11934,7 +11974,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12016,32 +12056,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12049,7 +12093,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12073,17 +12117,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12093,17 +12137,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12208,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12279,7 +12323,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12394,7 +12438,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12509,7 +12553,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12563,7 +12607,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -12624,7 +12668,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12678,7 +12722,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -12739,7 +12783,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12854,7 +12898,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12908,7 +12952,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -12969,7 +13013,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13023,7 +13067,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -13084,7 +13128,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13138,7 +13182,7 @@
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -13199,7 +13243,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13257,6 +13301,236 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr"/>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr"/>
+      <c r="R109" s="2" t="inlineStr"/>
+      <c r="S109" s="2" t="inlineStr"/>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z109" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA109" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB109" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC109" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr"/>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr"/>
+      <c r="R110" s="2" t="inlineStr"/>
+      <c r="S110" s="2" t="inlineStr"/>
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z110" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA110" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB110" s="2" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="AC110" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-03-浦东35路.xlsx
+++ b/data/export/2026-10-03-浦东35路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>118.3</t>
+          <t>119.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2506,17 +2506,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3680,17 +3680,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>118.3</t>
+          <t>119.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5703,17 +5703,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7968,17 +7968,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8692,7 +8692,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -9295,7 +9295,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>118.3</t>
+          <t>119.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9642,17 +9642,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -10189,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10427,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -11740,7 +11740,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -11832,24 +11832,24 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11908,12 +11908,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -11941,32 +11941,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11974,7 +11978,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11998,17 +12002,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12018,17 +12022,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -12066,24 +12070,24 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -12093,7 +12097,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12142,12 +12146,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -12175,32 +12179,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12208,7 +12216,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12232,17 +12240,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12252,12 +12260,12 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>118.3</t>
+          <t>119.2</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12290,12 +12298,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq61，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -12323,7 +12331,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12331,10 +12339,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q100" s="2" t="inlineStr"/>
-      <c r="R100" s="2" t="inlineStr"/>
-      <c r="S100" s="2" t="inlineStr"/>
-      <c r="T100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12377,7 +12401,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -12405,32 +12429,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12438,7 +12466,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12462,17 +12490,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12482,17 +12510,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -12553,7 +12581,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12635,12 +12663,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq56，推进28站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -12668,18 +12696,34 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>迎春路长柳路</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
           <t>20:21</t>
         </is>
       </c>
-      <c r="P103" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="Q103" s="2" t="inlineStr"/>
-      <c r="R103" s="2" t="inlineStr"/>
-      <c r="S103" s="2" t="inlineStr"/>
-      <c r="T103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq33映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U103" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12722,7 +12766,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12827,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12898,7 +12942,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12952,7 +12996,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -13013,7 +13057,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13128,7 +13172,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13182,7 +13226,7 @@
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -13243,7 +13287,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13297,7 +13341,7 @@
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -13358,7 +13402,7 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -13473,7 +13517,7 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
@@ -13527,7 +13571,7 @@
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-浦东35路.xlsx
+++ b/data/export/2026-10-03-浦东35路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>123.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2851,17 +2851,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3085,17 +3085,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4870,17 +4870,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>123.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5941,17 +5941,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6179,17 +6179,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8206,17 +8206,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -9295,7 +9295,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9652,7 +9652,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -9771,7 +9771,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9995,17 +9995,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10114,17 +10114,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10427,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10471,17 +10471,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>123.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11195,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -11740,7 +11740,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -12520,7 +12520,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -12635,7 +12635,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -12668,7 +12668,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq56，推进28站，达到≥2站确认条件</t>
+          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -12696,7 +12696,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -12909,32 +12909,36 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12942,7 +12946,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12966,17 +12970,17 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
@@ -12986,17 +12990,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.2</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -13024,32 +13028,36 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M106" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -13057,7 +13065,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13081,17 +13089,17 @@
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y106" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z106" s="2" t="inlineStr">
@@ -13101,17 +13109,17 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -13139,32 +13147,36 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M107" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -13172,7 +13184,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13196,17 +13208,17 @@
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X107" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y107" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z107" s="2" t="inlineStr">
@@ -13216,17 +13228,17 @@
       </c>
       <c r="AA107" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -13254,32 +13266,36 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>115分钟</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M108" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -13287,7 +13303,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13311,17 +13327,17 @@
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y108" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z108" s="2" t="inlineStr">
@@ -13331,17 +13347,17 @@
       </c>
       <c r="AA108" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>123.7</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -13369,32 +13385,36 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:42</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M109" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -13402,7 +13422,7 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -13426,17 +13446,17 @@
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y109" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z109" s="2" t="inlineStr">
@@ -13446,7 +13466,7 @@
       </c>
       <c r="AA109" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB109" s="2" t="inlineStr">
@@ -13517,7 +13537,7 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
@@ -13571,7 +13591,7 @@
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
